--- a/game20/web.xlsx
+++ b/game20/web.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectGames\game20\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>domain</t>
   </si>
@@ -45,34 +50,16 @@
     <t>json</t>
   </si>
   <si>
-    <t>fulminat.site</t>
-  </si>
-  <si>
-    <t>#c9a87a</t>
-  </si>
-  <si>
-    <t>frisket.fun</t>
-  </si>
-  <si>
-    <t>#ff88ff</t>
-  </si>
-  <si>
-    <t>deflagrate.site</t>
-  </si>
-  <si>
-    <t>#20b2aa</t>
-  </si>
-  <si>
-    <t>titubate.site</t>
-  </si>
-  <si>
-    <t>#98fb98</t>
-  </si>
-  <si>
-    <t>corrade.site</t>
-  </si>
-  <si>
-    <t>#ba55d3</t>
+    <t>play.voidspire.cloud</t>
+  </si>
+  <si>
+    <t>#ed6d46</t>
+  </si>
+  <si>
+    <t>sec.voidspire.cloud</t>
+  </si>
+  <si>
+    <t>#7d929f</t>
   </si>
   <si>
     <t>paly.sorrel.cloud</t>
@@ -139,7 +126,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -199,6 +186,21 @@
     </font>
     <font>
       <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -450,13 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9A87A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF88FF"/>
+        <fgColor rgb="FFED6D46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D929F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -789,28 +791,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -819,118 +812,127 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -988,22 +990,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1443,57 +1445,20 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
+      <c r="A5" s="21"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="21"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
+      <c r="A6" s="21"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="21"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="fulminat.site"/>
-    <hyperlink ref="A3" r:id="rId2" display="frisket.fun"/>
-    <hyperlink ref="A4" r:id="rId3" display="deflagrate.site"/>
-    <hyperlink ref="A5" r:id="rId4" display="titubate.site"/>
-    <hyperlink ref="A6" r:id="rId5" display="corrade.site"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1527,10 +1492,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1541,10 +1506,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1555,10 +1520,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1567,20 +1532,20 @@
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
@@ -1588,10 +1553,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1601,10 +1566,10 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="I7" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1614,10 +1579,10 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="I8" s="14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1627,10 +1592,10 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="I9" s="16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
